--- a/samples/ss_cbatu34_mdrcn_ingest.xlsx
+++ b/samples/ss_cbatu34_mdrcn_ingest.xlsx
@@ -709,25 +709,16 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -784,15 +775,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -859,15 +846,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -916,29 +899,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -977,25 +952,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1034,25 +1000,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1091,19 +1048,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1152,25 +1101,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1209,23 +1149,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>GI Simpul 4 subsistem; split busbar + kopel</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1274,25 +1207,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1331,25 +1255,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1388,19 +1303,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1449,25 +1356,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1506,25 +1404,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1563,25 +1452,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1620,25 +1500,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1677,25 +1548,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1734,25 +1596,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1791,25 +1644,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1866,19 +1710,16 @@
       <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1927,29 +1768,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1988,19 +1821,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2049,25 +1874,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2106,25 +1922,16 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2181,15 +1988,11 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2256,15 +2059,11 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2313,25 +2112,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2370,25 +2160,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2427,19 +2208,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2488,25 +2261,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2545,25 +2309,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2602,19 +2357,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2663,25 +2410,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2720,25 +2458,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2777,19 +2506,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2838,25 +2559,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2913,19 +2625,16 @@
       <c r="J38" t="n">
         <v>2</v>
       </c>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>IBT 150/70 kV</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2974,29 +2683,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3035,19 +2736,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3096,19 +2789,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3157,19 +2842,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3218,25 +2895,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3293,15 +2961,11 @@
       <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3368,15 +3032,11 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3425,25 +3085,16 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3500,19 +3151,16 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>IBT 2 150/66 kV; beda rasio, tidak paralel dengan IBT 1&amp;5</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3561,25 +3209,16 @@
           <t>66 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3618,23 +3257,16 @@
           <t>66 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>tegangan primer rendah (risiko 11)</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3683,19 +3315,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3744,19 +3368,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3805,17 +3421,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3831,7 +3441,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3870,17 +3479,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3896,7 +3499,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3935,17 +3537,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3961,7 +3557,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4000,17 +3595,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>batas ke Subsistem Sukatani 1,2</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -4026,7 +3615,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4065,17 +3653,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -4091,7 +3673,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4130,17 +3711,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -4156,7 +3731,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4195,17 +3769,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -4221,7 +3789,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4260,17 +3827,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -4286,7 +3847,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4325,17 +3885,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>batas ke Subsistem Bandung Selatan - New Ujungberung</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -4351,7 +3905,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4390,17 +3943,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>batas ke sisi Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -4416,7 +3963,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4533,7 +4079,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SUTT Cibatu 3,4 - Jababeka Usin</t>
@@ -4554,7 +4099,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -4568,8 +4112,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4596,7 +4138,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT Cibatu 3,4 - Cilegsi</t>
@@ -4617,7 +4158,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -4631,8 +4171,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4659,7 +4197,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Cibatu 3,4 - Hankook (arah SS Cibatu 1,2)</t>
@@ -4680,7 +4217,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -4694,8 +4230,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4747,7 +4281,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -4761,8 +4294,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4789,7 +4320,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Cibatu 3,4 - Kesambi Baru</t>
@@ -4810,7 +4340,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -4824,8 +4353,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4877,7 +4404,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -4891,8 +4417,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4919,7 +4443,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Pinayungan - Tegal Herang (arah SS Deltamas)</t>
@@ -4940,7 +4463,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -4954,8 +4476,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -4982,7 +4502,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Pinayungan - Mega Kaya (arah SS Deltamas)</t>
@@ -5003,7 +4522,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -5017,8 +4535,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5070,7 +4586,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -5084,8 +4599,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5112,7 +4625,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT Peruri - Purwamaya</t>
@@ -5133,7 +4645,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -5147,8 +4658,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5175,7 +4684,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>SUTT Purwamaya - Tanjung Jabe</t>
@@ -5196,7 +4704,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -5210,8 +4717,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5238,7 +4743,6 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Purwamaya - Honda</t>
@@ -5259,7 +4763,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -5273,8 +4776,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5301,7 +4802,6 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>SUTT Kesambi Baru - Katomukti</t>
@@ -5322,7 +4822,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -5336,8 +4835,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5364,7 +4861,6 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Kesambi Baru - Maligi</t>
@@ -5385,7 +4881,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -5399,8 +4894,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5427,7 +4920,6 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>SUTT Maligi - Indolakto Beauty</t>
@@ -5448,7 +4940,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -5462,8 +4953,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5490,7 +4979,6 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>SUTT Maligi - Karang Pawitan</t>
@@ -5511,7 +4999,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -5525,8 +5012,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5553,7 +5038,6 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT Kesambi Baru - Sukamedi (arah sisi Mandirancan)</t>
@@ -5574,7 +5058,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -5588,8 +5071,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5616,7 +5097,6 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT Kesambi Baru - Tegal Tanjung Baru</t>
@@ -5637,7 +5117,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -5651,8 +5130,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5679,7 +5156,6 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTT Tegal Tanjung Baru - Padalarang Baru (arah SS Cirata)</t>
@@ -5700,7 +5176,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -5714,8 +5189,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5742,7 +5215,6 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT Tegal Tanjung Baru - Dawuan</t>
@@ -5763,7 +5235,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -5777,8 +5248,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5805,7 +5274,6 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT Dawuan - Sukatani (arah SS Sukatani 1,2)</t>
@@ -5826,7 +5294,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -5840,8 +5307,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5868,7 +5333,6 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT 70 kV Dawuan - Pondok Ali</t>
@@ -5889,7 +5353,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -5903,8 +5366,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5956,7 +5417,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>1</v>
       </c>
@@ -5970,8 +5430,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -5998,7 +5456,6 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>SUTT 70 kV Rengasdengklok - Curug (arah SS Cirata)</t>
@@ -6019,7 +5476,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -6033,8 +5489,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6061,7 +5515,6 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTT 70 kV Pondok Ali - Indramayu Barat (arah SS Cirata)</t>
@@ -6082,7 +5535,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>1</v>
       </c>
@@ -6096,8 +5548,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6124,7 +5574,6 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>SUTT 70 kV Pondok Ali - Purwakarta (arah SS Cirata)</t>
@@ -6145,7 +5594,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -6159,8 +5607,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6187,7 +5633,6 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>Outlet PLTU Indramayu</t>
@@ -6208,7 +5653,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>1</v>
       </c>
@@ -6222,8 +5666,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6250,7 +5692,6 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>SUTT Indramayu - Kesambi Baru (arah sisi Cibatu 3,4)</t>
@@ -6271,7 +5712,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -6285,8 +5725,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6338,7 +5776,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -6352,8 +5789,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6380,7 +5815,6 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>SUTT Mandirancan - Narajiwa</t>
@@ -6401,7 +5835,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -6415,8 +5848,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6468,7 +5899,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -6482,8 +5912,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6510,7 +5938,6 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>SUTT Sukamedi - Haurgeulis</t>
@@ -6531,7 +5958,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -6545,8 +5971,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6573,7 +5997,6 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>SUTT Narajiwa - Jatibarang</t>
@@ -6594,7 +6017,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -6608,8 +6030,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6661,7 +6081,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -6675,8 +6094,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6703,7 +6120,6 @@
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>SUTT Haurgeulis - Cikedung</t>
@@ -6724,7 +6140,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>2</v>
       </c>
@@ -6738,8 +6153,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6766,7 +6179,6 @@
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>SUTT Jatibarang - Cikedung</t>
@@ -6787,7 +6199,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>2</v>
       </c>
@@ -6801,8 +6212,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6854,7 +6263,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>2</v>
       </c>
@@ -6868,8 +6276,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6921,7 +6327,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>1</v>
       </c>
@@ -6935,8 +6340,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -6988,7 +6391,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>1</v>
       </c>
@@ -7002,8 +6404,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7055,7 +6455,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -7069,8 +6468,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7097,7 +6494,6 @@
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>SUTT Seragi - Sunyaragi</t>
@@ -7118,7 +6514,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -7132,8 +6527,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7185,7 +6578,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -7199,8 +6591,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7252,7 +6642,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -7266,8 +6655,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7294,7 +6681,6 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>SUTT 70 kV Sunyaragi - Arjawinangun</t>
@@ -7315,7 +6701,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -7329,8 +6714,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7357,7 +6740,6 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>SUTT 66 kV Sunyaragi - Kuningan</t>
@@ -7378,7 +6760,6 @@
           <t>66 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -7392,8 +6773,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7420,7 +6799,6 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>SUTT 70 kV Kadipaten - Parakan (arah SS New Ujungberung)</t>
@@ -7441,7 +6819,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -7455,8 +6832,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -7582,7 +6957,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7626,7 +7000,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7670,7 +7043,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7714,7 +7086,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7758,7 +7129,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7802,7 +7172,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7846,7 +7215,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7890,7 +7258,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7934,7 +7301,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -7978,7 +7344,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>CBATU34</t>
@@ -8022,7 +7387,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>MDRCN</t>
@@ -8066,7 +7430,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>MDRCN</t>
@@ -8155,7 +7518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru-Sukatani Gobel). Sesuai RUPTL 2025-2034 COD 2025. 2. Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025-2034 COD 2025</t>
+          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru-Sukatani Gobel). Sesuai RUPTL 2025 -2034 COD 2025. 2. Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025 -2034 COD 2025</t>
         </is>
       </c>
     </row>
@@ -8190,7 +7553,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru-Sukatani Gobel). Sesuai RUPTL 2025-2034 COD 2025. 2. Rekonduktoring Outlet GITET Cibatu (Cibatu-Mekarsari- Pinayungan 1,2 ). Sesuai RUPTL 2025-2034 COD 2027</t>
+          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru-Sukatani Gobel). Sesuai RUPTL 2025 -2034 COD 2025. 2. Rekonduktoring Outlet GITET Cibatu (Cibatu-Mekarsari- Pinayungan 1,2 ). Sesuai RUPTL 2025 -2034 COD 2027</t>
         </is>
       </c>
     </row>
@@ -8225,7 +7588,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru-Sukatani Gobel). Sesuai RUPTL 2025-2034 COD 2025. Progres: 51,06% (info pada Rakor Ophar Jabar 16Maret 2026). Prioritas: P0 (Pemadaman Tahap-1 dilaksanakan mulai 19 Agustus 2025 s.d 19 Nov 2025). 2. Rekonduktoring Outlet GITET Cibatu (Cibatu-Mekarsari- Pinayungan 1,2). Sesuai RUPTL 2025-2034 COD 2027</t>
+          <t>Jangka Pendek: 1. Rekonduktoring Outlet GITET Sukatani (Kosambi Baru-Sukatani Gobel). Sesuai RUPTL 2025 -2034 COD 2025. Progres: 51,06% (info pada Rakor Ophar Jabar 16Maret 2026). Prioritas: P0 (Pemadaman Tahap-1 dilaksanakan mulai 19 Agustus 2025 s.d 19 Nov 2025). 2. Rekonduktoring Outlet GITET Cibatu (Cibatu-Mekarsari- Pinayungan 1,2). Sesuai RUPTL 2025 -2034 COD 2027</t>
         </is>
       </c>
     </row>
@@ -8295,7 +7658,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Percepatan pembangunan GI 150 kV Rengasdengklok Baru, untuk mengambil sebagian beban GI 70 kV Rengasdengklok. Sesuai RUPTL 2025 -2034, COD 2026</t>
+          <t>Jangka Pendek: Percepatan pembangunan GI 150 kV Rengasdengklok Baru, untuk mengambil sebagian beban GI 70 kV Rengasdengklok. Sesuai RUPTL 2025 - 2034, COD 2026</t>
         </is>
       </c>
     </row>
@@ -8330,7 +7693,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Percepatan pembangunan GI 150 kV Rengasdengklok Baru, untuk mengambil sebagian beban GI 70 kV Rengasdengklok. Sesuai RUPTL 2025-2034, COD 2026. 2. Pembangunan Double Busbar GI Rengasdengklok. COD 2026. Progres : 60% (Info pada Rakor Ophar Jabar 21 April 2026)</t>
+          <t>Jangka Pendek: 1. Percepatan pembangunan GI 150 kV Rengasdengklok Baru, untuk mengambil sebagian beban GI 70 kV Rengasdengklok. Sesuai RUPTL 2025 -2034, COD 2026. 2. Pembangunan Double Busbar GI Rengasdengklok. COD 2026. Progres : 60% (Info pada Rakor Ophar Jabar 21 April 2026)</t>
         </is>
       </c>
     </row>
@@ -8365,7 +7728,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025- 2034 COD 2025</t>
+          <t>Jangka Pendek: Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025 - 2034 COD 2025</t>
         </is>
       </c>
     </row>
@@ -8400,7 +7763,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan extension IBT ke- 3&amp;4 Pemalang/New Batang beserta SUTT 150 kV New Batang-Comal dan SUTT 150 kV New Batang-KIT Batang.Sesuai- 2033, COD 2027). 2. Rekonduktoring SUTT 150 kV Kalibakal-Bumiayu menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2027). 3. Rekonduktoring SUTT 150 kV Bumiayu-Balapulang menjadi Usulan / Solusi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2027). 4. Usulan pembangunan IBT-3,4 Pemalang dan outlet terkait. Diusulkan COD Tahun 2028 5. Usulan baru uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027</t>
+          <t>Jangka Pendek: 1. Pembangunan extension IBT ke- 3&amp;4 Pemalang/New Batang beserta SUTT 150 kV New Batang-Comal dan SUTT 150 kV New Batang-KIT Batang. Sesuai- 2033, COD 2027). 2. Rekonduktoring SUTT 150 kV Kalibakal-Bumiayu menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2027). 3. Rekonduktoring SUTT 150 kV Bumiayu-Balapulang menjadi Usulan / Solusi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2027). 4. Usulan pembangunan IBT-3,4 Pemalang dan outlet terkait. Diusulkan COD Tahun 2028 5. Usulan baru uprating Kapasitor GI 150 kV Kebasen dari 25 MVAR menjadi 50 MVAR. Lalu kapasitor ex-GI 150 kV Kebasen 25 MVAR direlokasi ke GI 150 kV Balapulang, diusulkan COD 2027</t>
         </is>
       </c>
     </row>
@@ -8435,7 +7798,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025- 2034 COD 2025</t>
+          <t>Jangka Pendek: Pembangunan IBT GITET Indramayu dan outletnya. Sesuai RUPTL 2025 - 2034 COD 2025</t>
         </is>
       </c>
     </row>
@@ -8530,7 +7893,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload IBT (dalam kondisi normal). 2.Berpotensi padam82MW apabila trip 1 IBT (N- 1). 3.Fleksibilitas operasi dan keandalan menjadi berkurang 4.Kesulitan dalam melaksanakan pemeliharaan</t>
+          <t>1.Terjadi Overload IBT (dalam kondisi normal). 2.Berpotensi padam 82MW apabila trip 1 IBT (N- 1). 3.Fleksibilitas operasi dan keandalan menjadi berkurang 4.Kesulitan dalam melaksanakan pemeliharaan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8540,7 +7903,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan Outlet GI 150 kV Balongan memotong SUTT Jatibarang-Arjawinangun. Sesuai RUPTL 2025-2034, COD 2025. 2. Perkuatan pasokan GI Semen yaitu : a.Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. b.Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Disuslkan COD 2027</t>
+          <t>Jangka Pendek : 1. Pembangunan Outlet GI 150 kV Balongan memotong SUTT Jatibarang-Arjawinangun. Sesuai RUPTL 2025-2034, COD 2025. 2. Perkuatan pasokan GI Semen yaitu : a.Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. b.Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Disuslkan COD 2027</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8008,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Perkuatan pasokan GI Semen yaitu : -Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. atau - Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Diusulkan COD 2027</t>
+          <t>Jangka Pendek: Perkuatan pasokan GI Semen yaitu : - Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. atau - Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Diusulkan COD 2027</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8043,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Perkuatan pasokan GI Semen yaitu : -Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. atau - Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Diusulkan COD 2027</t>
+          <t>Jangka Pendek: Perkuatan pasokan GI Semen yaitu : - Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. atau - Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Diusulkan COD 2027</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8078,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Perkuatan pasokan GI Semen yaitu : -Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. atau - Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Disuslkan COD 2027</t>
+          <t>Jangka Pendek: Perkuatan pasokan GI Semen yaitu : - Usulan Penambahan IBT 150/70 kV di GI 150 kV New Arjawinangun, diusulkan COD 2027. atau - Usulan Pembangunan GI 150 kV Semen untuk mengakomodir KTT Semen, Disuslkan COD 2027</t>
         </is>
       </c>
     </row>
